--- a/Mapeo - Rendicion de cuentas.xlsx
+++ b/Mapeo - Rendicion de cuentas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RicardoCastellanos\Dashboard_CGTGE\Dashboard_CGTGEv2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F817078-A227-4119-8EAC-63137BE0688C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274C0BBD-C834-4E26-9A68-F375CEC0BF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0B68A3EE-84B7-4A2A-921D-E4F05FC3CD15}"/>
   </bookViews>
@@ -226,31 +226,6 @@
     <t>Dirección De Seguimiento Y Evaluación De La Gestión De Emprendimientos, Artes E Innovación</t>
   </si>
   <si>
-    <r>
-      <t>Profesionales DECE (Apoyo Psicológico) (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>agregar brecha reducida</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Reunion con VALE, sobre hitos del MINEDEC, y que ella recomiende si incluir mas sobre hitos. </t>
   </si>
   <si>
@@ -261,6 +236,9 @@
   </si>
   <si>
     <t>MeCapacito (Docentes Capacitados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profesionales DECE (Apoyo Psicológico) </t>
   </si>
 </sst>
 </file>
@@ -860,7 +838,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3">
         <v>120</v>
@@ -894,7 +872,7 @@
         <v>37</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3">
         <v>122296</v>
@@ -911,7 +889,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3">
         <v>2289</v>
@@ -1109,12 +1087,12 @@
     </row>
     <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="C23" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B26" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
